--- a/public/exports-with-coowners/65307316.xlsx
+++ b/public/exports-with-coowners/65307316.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-with-coowners/65307316.xlsx
+++ b/public/exports-with-coowners/65307316.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055254</t>
+          <t xml:space="preserve">200055256</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821094</t>
+          <t xml:space="preserve">311821096</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">OS Engineering ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M92" t="inlineStr">

--- a/public/exports-with-coowners/65307316.xlsx
+++ b/public/exports-with-coowners/65307316.xlsx
@@ -889,7 +889,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">200055256</t>
+          <t xml:space="preserve">200055254</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821096</t>
+          <t xml:space="preserve">311821094</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OS Engineering ApS</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
